--- a/output/full_scan/batch_seq0_2026-08-27.xlsx
+++ b/output/full_scan/batch_seq0_2026-08-27.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>949.3679345871705</v>
+        <v>1149.36793458717</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>494</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.0832962804372</v>
+        <v>64.08329628167991</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.66939176473207</v>
+        <v>20.66939178632694</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.536793458717032</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>14.07919637714167</v>
+        <v>14.07919637689364</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>9912</v>
+        <v>8996</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>760.4034011658674</v>
+        <v>1146.928703504476</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.2</v>
+        <v>1310</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>68.17735764766412</v>
+        <v>61.05980240428883</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11.24425106471369</v>
+        <v>19.08921167409067</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.322927006560957</v>
+        <v>1.875717912922901</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0352529283406676</v>
+        <v>19.31652063026305</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8996</v>
+        <v>8103</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>756.9287035044764</v>
+        <v>1036.513897942012</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1310</v>
+        <v>114</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>61.05980239638311</v>
+        <v>79.07989292169447</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19.08921158842437</v>
+        <v>33.86113139370566</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.875717912922901</v>
+        <v>3.251389794201232</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>19.31652063245718</v>
+        <v>4.211470755856776</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8271</v>
+        <v>8046</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>732.2821990913325</v>
+        <v>919.5405410050834</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>234</v>
+        <v>1295</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.95613518518965</v>
+        <v>60.13665395608314</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.23185513299336</v>
+        <v>11.66136887305202</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5793967043385096</v>
+        <v>0.8207138773193543</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.716416158904841</v>
+        <v>2.867334707771768</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8103</v>
+        <v>8222</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>716.5138979420124</v>
+        <v>881.8424546885575</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>114</v>
+        <v>40.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>79.07989289765368</v>
+        <v>58.3003133910411</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>33.861131346066</v>
+        <v>25.56512539786726</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.251389794201232</v>
+        <v>2.198514841418192</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.211470756232814</v>
+        <v>0.1332075809414497</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>683.5424963571849</v>
+        <v>873.5424963571811</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>289</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>63.73338068845747</v>
+        <v>63.73338067354123</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14.07215738876922</v>
+        <v>14.0721573909299</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.262138520984184</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.28224488533657</v>
+        <v>3.282244886195132</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8155</v>
+        <v>8085</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>675.2823985310976</v>
+        <v>859.4238366390596</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>364.5</v>
+        <v>15.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.00812028690274</v>
+        <v>81.92992810608281</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19.8386533290878</v>
+        <v>25.33325951081479</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.128239853109752</v>
+        <v>4.542383663905953</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>6.995820884313426</v>
+        <v>0.4308836263179794</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8085</v>
+        <v>8473</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>659.4238366390596</v>
+        <v>859.2668142393782</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.3</v>
+        <v>46.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>81.92992820862872</v>
+        <v>58.88600345104894</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.33325952110162</v>
+        <v>23.27758864061345</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.542383663905953</v>
+        <v>0.7567712581639796</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4308836263370592</v>
+        <v>0.3758865635636504</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8222</v>
+        <v>8155</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>646.8424546885574</v>
+        <v>845.2823985310976</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>40.8</v>
+        <v>364.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.30031329287826</v>
+        <v>66.00812026812289</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25.5651253648847</v>
+        <v>19.83865340944056</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.198514841418192</v>
+        <v>3.128239853109752</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1332075812848763</v>
+        <v>6.995820884218031</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8046</v>
+        <v>9912</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>634.5405410050836</v>
+        <v>780.4034011658674</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1295</v>
+        <v>13.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.13665395862626</v>
+        <v>68.1773576105644</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.66136890025887</v>
+        <v>11.24425121362519</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8207138773193543</v>
+        <v>3.322927006560957</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.867334707390178</v>
+        <v>0.0352529283311278</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9905</v>
+        <v>8271</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>604.5432281484774</v>
+        <v>742.2821990913326</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>21.45</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.47287508100174</v>
+        <v>56.95613521629372</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>19.40942874493678</v>
+        <v>24.23185528288486</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6215805429236514</v>
+        <v>0.5793967043385096</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0037524314849787</v>
+        <v>-0.716416159324603</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8182</v>
+        <v>8438</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>601.8987158289564</v>
+        <v>686.6883891252916</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>40.65</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>48.88862908273539</v>
+        <v>56.01337770589465</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10.25321305274296</v>
+        <v>19.34277949392822</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4863222174731834</v>
+        <v>1.298040608476857</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>3</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.3825743993337832</v>
+        <v>1.418463851788692</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8462</v>
+        <v>8104</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>601.7407369025216</v>
+        <v>636.4304034846986</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>174</v>
+        <v>31.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.31938335150365</v>
+        <v>47.92325224589243</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>42.65412124529067</v>
+        <v>26.8541200832312</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2252819944924099</v>
+        <v>1.51371369996146</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.7530656604162091</v>
+        <v>0.3106478397834842</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8473</v>
+        <v>9905</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>559.2668142393782</v>
+        <v>624.5432281484774</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46.4</v>
+        <v>21.45</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.88600336188245</v>
+        <v>59.47287511152129</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.27758860890653</v>
+        <v>19.40942865456438</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7567712581639796</v>
+        <v>0.6215805429236514</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.3758865637925925</v>
+        <v>0.0037524314754372</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8112</v>
+        <v>8093</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>505.4193737614086</v>
+        <v>623.7909815506583</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>92.2</v>
+        <v>27.25</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.10731579852829</v>
+        <v>59.80672942016141</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.77044068714282</v>
+        <v>16.76484136978006</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3464385225815337</v>
+        <v>0.7348765217618553</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.0573701792001153</v>
+        <v>0.4149557235405519</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>9105</v>
+        <v>8462</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>503.8259706547132</v>
+        <v>621.7407369025216</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>174</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.1890358564024</v>
+        <v>58.31938336488015</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15.5169283821714</v>
+        <v>42.65412125906592</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.623678645063629</v>
+        <v>0.2252819944924099</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0201479494466494</v>
+        <v>-0.7530656605115826</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8442</v>
+        <v>8431</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>488.8537942068164</v>
+        <v>613.3663311143076</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46.1</v>
+        <v>47.4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.20870549173269</v>
+        <v>49.18636977703565</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.2673940226225</v>
+        <v>11.66537173086845</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.360118288155544</v>
+        <v>1.319503148153115</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2398433194763387</v>
+        <v>0.0241043223091786</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8440</v>
+        <v>8249</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>482.6688808631377</v>
+        <v>606.4867571571224</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>20.65</v>
+        <v>42</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.01272051326215</v>
+        <v>48.84919509764279</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.83980228285535</v>
+        <v>25.14931762006512</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7175606897091398</v>
+        <v>0.6838895288489518</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1504377678364689</v>
+        <v>0.2412640166201798</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8464</v>
+        <v>8182</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>479.5720126918416</v>
+        <v>601.8987158289564</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>368.5</v>
+        <v>40.65</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>48.25208562546593</v>
+        <v>48.88862909493552</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.09286127921332</v>
+        <v>10.25321301690458</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5098658746024776</v>
+        <v>0.4863222174731834</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.833930597806958</v>
+        <v>0.3825743992670091</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8431</v>
+        <v>8299</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>473.3663311143076</v>
+        <v>595.4116257896491</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>47.4</v>
+        <v>2155</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>49.18636976452832</v>
+        <v>56.53413285833502</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11.66537170392326</v>
+        <v>12.9778631013517</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.319503148153115</v>
+        <v>0.7776040006655165</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0241043224904344</v>
+        <v>19.98833720848621</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8091</v>
+        <v>8240</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>469.7397157698022</v>
+        <v>578.2619220684838</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>218</v>
+        <v>45.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>41.64682551159336</v>
+        <v>58.94511828273298</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.9511505473934</v>
+        <v>27.22959626922269</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5758288786788796</v>
+        <v>4.925816255962647</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.11916283507413</v>
+        <v>0.7355937299575761</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8121</v>
+        <v>8147</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>460.4767956766527</v>
+        <v>538.9012845444696</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>28.1</v>
+        <v>125.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>38.26275072041535</v>
+        <v>50.26834892300445</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.0398361258244</v>
+        <v>26.86768400176189</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6744528164311077</v>
+        <v>0.6800132129790267</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.358596360947931</v>
+        <v>1.058723370607141</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9955</v>
+        <v>8064</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>454.2030815084888</v>
+        <v>531.4436170092542</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>25</v>
+        <v>104.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.96095852217659</v>
+        <v>49.33605466572526</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.73700379474094</v>
+        <v>18.73979730084727</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8851589184507748</v>
+        <v>1.039319356216769</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1510987220324688</v>
+        <v>1.3926644274339</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8932</v>
+        <v>8074</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>448.2829048990818</v>
+        <v>531.2537720089522</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>48.04323617959472</v>
+        <v>52.26574611137473</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12.84261193236396</v>
+        <v>17.69127240438527</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.610360646829206</v>
+        <v>0.9715498990768257</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.6383048127280473</v>
+        <v>0.6043802616418168</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8213</v>
+        <v>8081</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>446.5660563485626</v>
+        <v>525.0915462515748</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>33.15</v>
+        <v>261.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.04290621176548</v>
+        <v>50.77707635590197</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.60428593732448</v>
+        <v>17.25178471600178</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.270182192650762</v>
+        <v>0.4713151361431299</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2089053521154986</v>
+        <v>1.049755141558535</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8097</v>
+        <v>8111</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>445.1301638616216</v>
+        <v>525.0899284778125</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>49.25</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>30.07704332210452</v>
+        <v>58.87220031907658</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24.58650552576752</v>
+        <v>19.69678386773026</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3538207836544221</v>
+        <v>0.981179864257254</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0067356938623623</v>
+        <v>0.5745159597565723</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8299</v>
+        <v>8390</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>424.9099708130448</v>
+        <v>524.9416243641031</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2155</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.53413284899107</v>
+        <v>54.83124830061384</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12.97786299312996</v>
+        <v>16.59555972890965</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7413199726095396</v>
+        <v>1.018355261360823</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>2</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>19.98833721153908</v>
+        <v>0.7211415242311481</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8147</v>
+        <v>9105</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>423.9012845444698</v>
+        <v>523.8259706547133</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.26834892300445</v>
+        <v>49.18903575517896</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26.86768400176189</v>
+        <v>15.51692838486008</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6800132129790267</v>
+        <v>0.623678645063629</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.058723370702548</v>
+        <v>0.0201479494580948</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8093</v>
+        <v>8150</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>423.7909815506584</v>
+        <v>515.053397876252</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>27.25</v>
+        <v>90.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.80672940905822</v>
+        <v>49.74330232163799</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16.7648413153482</v>
+        <v>10.16074360332018</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7348765217618553</v>
+        <v>0.4573497101296611</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4149557236549972</v>
+        <v>0.5782684744780249</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8482</v>
+        <v>8110</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>419.9811895331517</v>
+        <v>514.7048708662848</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>48.25</v>
+        <v>46.15</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.73413812319833</v>
+        <v>52.53796674104134</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3.996951382987678</v>
+        <v>10.20686719638589</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.187982323915536</v>
+        <v>0.548447274195897</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1019541592080628</v>
+        <v>0.3975489265905998</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8105</v>
+        <v>8162</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>419.6163629894038</v>
+        <v>512.4103129853197</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15.15</v>
+        <v>62.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>40.43125625294154</v>
+        <v>54.29233390356649</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.21766335826608</v>
+        <v>21.78921010736561</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5109455759414449</v>
+        <v>1.09374558358959</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0432142843516002</v>
+        <v>1.521167657680655</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>9930</v>
+        <v>8071</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>417.838022572926</v>
+        <v>507.483669283302</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>63.1</v>
+        <v>24.4</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.13909472943583</v>
+        <v>51.64672378633528</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.69394396821709</v>
+        <v>14.37129938373012</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.865914266502352</v>
+        <v>0.7689733934053479</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1853821431826578</v>
+        <v>0.1789630962263744</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8109</v>
+        <v>8215</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>416.3597073265215</v>
+        <v>503.5123105386869</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>130.5</v>
+        <v>24.85</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.68517556795965</v>
+        <v>50.96713471099593</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16.97698307651965</v>
+        <v>26.80664771172184</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.214114906625822</v>
+        <v>1.309087809204649</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0345687544987025</v>
+        <v>0.1620213248270976</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8074</v>
+        <v>8291</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>416.2537720089521</v>
+        <v>499.0759753956703</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>57</v>
+        <v>36.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.26574610570555</v>
+        <v>48.20188761169385</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.69127238270681</v>
+        <v>12.02438361736552</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9715498990768257</v>
+        <v>1.078863062023327</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.6043802616608935</v>
+        <v>0.0945934501467546</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8150</v>
+        <v>8112</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>410.053397876252</v>
+        <v>495.4193737614086</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>90.3</v>
+        <v>92.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.74330232163799</v>
+        <v>52.10731580227283</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10.16074360635203</v>
+        <v>12.770440682636</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4573497101296611</v>
+        <v>0.3464385225815337</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.5782684745638793</v>
+        <v>-0.0573701793909036</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8390</v>
+        <v>9930</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>409.941624364103</v>
+        <v>492.838022572926</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>101</v>
+        <v>63.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.83124828777173</v>
+        <v>46.13909466380752</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.59555963833737</v>
+        <v>30.69394405999403</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.018355261360823</v>
+        <v>0.865914266502352</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.7211415243265367</v>
+        <v>0.1853821432017386</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8240</v>
+        <v>8234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>408.2619220684828</v>
+        <v>492.3776732191434</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>45.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.94511827661842</v>
+        <v>53.14530962493014</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>27.22959625783441</v>
+        <v>18.54492511399516</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.925816255962647</v>
+        <v>0.703484853278147</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.7355937300243611</v>
+        <v>-0.07202827697008379</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, bb_squeeze_breakout, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8043</v>
+        <v>8086</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>407.2197392642151</v>
+        <v>488.996597998642</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.6954348610635</v>
+        <v>48.90550325792088</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.81852970961463</v>
+        <v>23.50217223512991</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9598689972000488</v>
+        <v>1.361926605520963</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.7092680148591448</v>
+        <v>1.034968737973403</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8438</v>
+        <v>8442</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>406.6883891252916</v>
+        <v>488.8537942068168</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>46.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>56.01337769212273</v>
+        <v>54.20870555721832</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19.34277936470656</v>
+        <v>23.26739425914248</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.298040608476857</v>
+        <v>1.360118288155544</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.418463851969955</v>
+        <v>0.2398433193046226</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8081</v>
+        <v>8092</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>405.0915462515748</v>
+        <v>484.4635392302097</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>261.5</v>
+        <v>13.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.77707636573229</v>
+        <v>55.80917506633634</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.25178469226886</v>
+        <v>21.84774357400587</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4713151361431299</v>
+        <v>0.5632656147805737</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.049755141653946</v>
+        <v>0.1587438675557841</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8104</v>
+        <v>8440</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>401.4304034846986</v>
+        <v>482.6688808631383</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>31.8</v>
+        <v>20.65</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.92325214353598</v>
+        <v>58.01272060103958</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>26.8541200602167</v>
+        <v>21.83980228304645</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.51371369996146</v>
+        <v>0.7175606897091398</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.3106478399742831</v>
+        <v>0.1504377676647575</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8422</v>
+        <v>8464</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>397.3803550243844</v>
+        <v>479.5720126918416</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>27</v>
+        <v>368.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.23911709192102</v>
+        <v>48.25208563342896</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13.69892588958262</v>
+        <v>21.09286128603205</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7617233268604702</v>
+        <v>0.5098658746024776</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1046660884524977</v>
+        <v>-1.833930598570104</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8071</v>
+        <v>9955</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>392.483669283302</v>
+        <v>474.2030815084888</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.64672373494925</v>
+        <v>53.96095861102032</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.3712990580852</v>
+        <v>21.73700390993714</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7689733934053479</v>
+        <v>0.8851589184507748</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1789630963885507</v>
+        <v>0.151098721889376</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8064</v>
+        <v>8091</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>391.4436170092543</v>
+        <v>469.7397157698022</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>104.5</v>
+        <v>218</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.33605469485254</v>
+        <v>41.64682554415735</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.73979738094944</v>
+        <v>14.95115060152432</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.039319356216769</v>
+        <v>0.5758288786788796</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.392664427443429</v>
+        <v>0.1191628343109467</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8111</v>
+        <v>8213</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>385.0899284778125</v>
+        <v>466.5660563485626</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>33.15</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.8722003369645</v>
+        <v>55.04290625124283</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.69678389171473</v>
+        <v>21.60428594552303</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.981179864257254</v>
+        <v>1.270182192650762</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.5745159598615128</v>
+        <v>0.2089053520487239</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8249</v>
+        <v>8374</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>381.4867571571223</v>
+        <v>461.3823291040857</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>42</v>
+        <v>83.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.84919504981788</v>
+        <v>52.15688357812278</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.14931756948412</v>
+        <v>16.69499029965439</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6838895288489518</v>
+        <v>0.7580225355824987</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.2412640169445281</v>
+        <v>0.1000461388834665</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8234</v>
+        <v>8121</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>377.3776732191428</v>
+        <v>460.4767956766527</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.14530965347648</v>
+        <v>38.26275071052606</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.54492500425293</v>
+        <v>30.03983613234214</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.703484853278147</v>
+        <v>0.6744528164311077</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>2</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.07202827666481069</v>
+        <v>0.3585963608429905</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8443</v>
+        <v>8926</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>376.7634549840104</v>
+        <v>457.8698746346896</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>11.4</v>
+        <v>57.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.43106966073533</v>
+        <v>40.50485570898469</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>40.89979776093744</v>
+        <v>31.16850792816242</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.3909040014069198</v>
+        <v>0.3960639480319896</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.008061749519856901</v>
+        <v>0.4413848010735899</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8086</v>
+        <v>9136</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>373.9965979986416</v>
+        <v>457.4471046156461</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>118</v>
+        <v>11.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.90550323032311</v>
+        <v>52.81090686858979</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.50217223039317</v>
+        <v>9.773765660750165</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.361926605520963</v>
+        <v>1.811874710676585</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>1</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.034968738660283</v>
+        <v>0.048552498571272</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8162</v>
+        <v>8054</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>372.4103129853198</v>
+        <v>452.9026581280781</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>62.8</v>
+        <v>84</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.29233390585685</v>
+        <v>47.04543036724554</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21.78921007082252</v>
+        <v>19.08794174593666</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.09374558358959</v>
+        <v>0.6531188879529009</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.521167657671119</v>
+        <v>0.9877655545915632</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8110</v>
+        <v>8261</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>369.7048708662848</v>
+        <v>450.9662058194508</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>46.15</v>
+        <v>185</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.53796672707249</v>
+        <v>45.28996478650744</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.20686720249878</v>
+        <v>17.067761050912</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.548447274195897</v>
+        <v>0.5870701781651105</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3975489266859945</v>
+        <v>2.35768328933224</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8215</v>
+        <v>8932</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>368.5123105386869</v>
+        <v>448.2829048990819</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>24.85</v>
+        <v>105</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.96713466950082</v>
+        <v>48.04323630698398</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>26.80664764782338</v>
+        <v>12.84261219556741</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.309087809204649</v>
+        <v>2.610360646829206</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1620213249606527</v>
+        <v>0.6383048099486556</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>9902</v>
+        <v>8097</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>361.4111996199049</v>
+        <v>445.1301638616215</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>13.85</v>
+        <v>49.25</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.67494374091847</v>
+        <v>30.07704332210452</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9.407701237103346</v>
+        <v>24.586505530071</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4476891962523937</v>
+        <v>0.3538207836544221</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0073310251142819</v>
+        <v>0.0067356936715667</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8088</v>
+        <v>8482</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>358.9453645280623</v>
+        <v>439.9811895331522</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>45.9</v>
+        <v>48.25</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.37814332764304</v>
+        <v>50.73413812439272</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.02963863483912</v>
+        <v>3.996951396406232</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3626474754768315</v>
+        <v>1.187982323915536</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>2</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2500248035691608</v>
+        <v>0.1019541590172701</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8481</v>
+        <v>8404</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>357.2849296553679</v>
+        <v>433.417512058649</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>41.2</v>
+        <v>16.35</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>55.31009806791118</v>
+        <v>49.42419165023918</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.47333533931902</v>
+        <v>14.62125148355823</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9090259786638616</v>
+        <v>1.023293251282767</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1039725458414196</v>
+        <v>0.0461052190006092</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8289</v>
+        <v>8429</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>354.235567673338</v>
+        <v>428.8053914667129</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>47</v>
+        <v>6.03</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.24567037707627</v>
+        <v>45.29064195245547</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.95285151194074</v>
+        <v>9.583260899313974</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6474599746208418</v>
+        <v>0.7623829802689525</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.6722167693402938</v>
+        <v>0.0121135253934702</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8374</v>
+        <v>8059</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>351.382329104087</v>
+        <v>420.3403265977319</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>83.2</v>
+        <v>14.15</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.15688366965345</v>
+        <v>44.64811826966484</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.69499020499734</v>
+        <v>20.83308075488976</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7580225355824987</v>
+        <v>1.958289405857469</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1000461389788619</v>
+        <v>0.0766841440903276</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8926</v>
+        <v>8105</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>347.8698746346896</v>
+        <v>419.6163629894037</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>57.4</v>
+        <v>15.15</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>40.50485567842179</v>
+        <v>40.43125632710315</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>31.16850792816242</v>
+        <v>27.21766341058185</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3960639480319896</v>
+        <v>0.5109455759414449</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.4413848011212922</v>
+        <v>-0.0432142844121515</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8463</v>
+        <v>8109</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>343.1286376250527</v>
+        <v>416.3597073265215</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>21.45</v>
+        <v>130.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>55.45094437833354</v>
+        <v>50.68517558164174</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.06320727976878</v>
+        <v>16.97698309501208</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6544149311475957</v>
+        <v>1.214114906625822</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0599416448487296</v>
+        <v>0.0345687544032761</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8096</v>
+        <v>8227</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>340.900390729299</v>
+        <v>415.0644796846107</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>40.35029754903746</v>
+        <v>52.24874443300378</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.96106805499399</v>
+        <v>19.0737730883511</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7335143057935072</v>
+        <v>1.430728074841213</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.2555578557875142</v>
+        <v>2.73956489681738</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>9904</v>
+        <v>8043</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>340.7806306431189</v>
+        <v>407.2197392642151</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>24.8</v>
+        <v>142</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.22960311441348</v>
+        <v>49.69543489220136</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.31354321439044</v>
+        <v>16.81852968356296</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6276287001956103</v>
+        <v>0.9598689972000488</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0980505682471822</v>
+        <v>0.7092680146874315</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8080</v>
+        <v>8101</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>335.4888240288068</v>
+        <v>399.7149329899366</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>28</v>
+        <v>12.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.45673142050386</v>
+        <v>52.03311814931963</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>52.72299804188831</v>
+        <v>9.355164511400613</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.0452113766954266</v>
+        <v>0.5714932989936568</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0109362986705716</v>
+        <v>0.4017465717723978</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8183</v>
+        <v>8163</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>333.5809977946423</v>
+        <v>398.7306218873344</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>29.2</v>
+        <v>31.55</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.56149584480954</v>
+        <v>45.30944125270876</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.13929648885623</v>
+        <v>18.98381633614558</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.171596544242988</v>
+        <v>0.6148577139989552</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>3</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0457797253001239</v>
+        <v>0.2503726265692139</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8367</v>
+        <v>8422</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>332.7371134701024</v>
+        <v>397.3803550243844</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>40.5</v>
+        <v>27</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.91990411218764</v>
+        <v>53.23911709192102</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>27.67162690269544</v>
+        <v>13.69892591769432</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2954830152531132</v>
+        <v>0.7617233268604702</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0376126452955266</v>
+        <v>0.1046660881255083</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8131</v>
+        <v>8478</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>324.9807687420521</v>
+        <v>382.8402760812414</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>63.3</v>
+        <v>144.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.19884170120535</v>
+        <v>45.68769078663274</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7.927362902889556</v>
+        <v>12.48669499526862</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5302667811803669</v>
+        <v>0.5002883307443348</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.2934279106774224</v>
+        <v>0.2216152648695315</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8404</v>
+        <v>8443</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>323.417512058647</v>
+        <v>376.7634549840104</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>16.35</v>
+        <v>11.4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.42419157870114</v>
+        <v>47.43106984295612</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.62125150029734</v>
+        <v>40.89979782936869</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.023293251282767</v>
+        <v>0.3909040014069198</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0461052190864648</v>
+        <v>-0.008061749548476899</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8455</v>
+        <v>8383</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>322.7554050123621</v>
+        <v>373.1570475092663</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>23.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.71845461203669</v>
+        <v>47.5850160111141</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.70912309452375</v>
+        <v>14.1453062605869</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3760211323876402</v>
+        <v>1.340572038769848</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.08305409157052999</v>
+        <v>-0.3440503367971832</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8423</v>
+        <v>8463</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>319.3088743010575</v>
+        <v>363.1286376250528</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>17.85</v>
+        <v>21.45</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.06580283810867</v>
+        <v>55.45094447739554</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>17.28787197858005</v>
+        <v>18.06320726084108</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2906175812313882</v>
+        <v>0.6544149311475957</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.001061064288599</v>
+        <v>0.059941644810569</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>9136</v>
+        <v>9902</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>317.4471046156461</v>
+        <v>361.4111996199049</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>11.8</v>
+        <v>13.85</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.81090687233493</v>
+        <v>52.67494383278849</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9.773765634315524</v>
+        <v>9.407701259096717</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.811874710676585</v>
+        <v>0.4476891962523937</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.048552498571272</v>
+        <v>0.0073310249902667</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8261</v>
+        <v>8088</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>315.9662058194509</v>
+        <v>358.9453645280623</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>185</v>
+        <v>45.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.28996478213357</v>
+        <v>42.37814333207729</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.06776098005416</v>
+        <v>14.02963868886309</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5870701781651105</v>
+        <v>0.3626474754768315</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>2.357683289675677</v>
+        <v>0.2500248033306667</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8092</v>
+        <v>8481</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>314.4635392302097</v>
+        <v>357.284929655368</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>13.6</v>
+        <v>41.2</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>55.80917500759051</v>
+        <v>55.31009831385688</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.84774355834641</v>
+        <v>12.47333560429416</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5632656147805737</v>
+        <v>0.9090259786638616</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1587438676034817</v>
+        <v>0.1039725452785744</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8054</v>
+        <v>8171</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>312.9026581280781</v>
+        <v>356.9381112009582</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>84</v>
+        <v>20.05</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.0454302441668</v>
+        <v>51.18127955418441</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.08794173124129</v>
+        <v>11.79177756509164</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6531188879529009</v>
+        <v>1.296275099057571</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.987765555736332</v>
+        <v>0.1024036667614192</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>9103</v>
+        <v>8289</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>309.8262021796367</v>
+        <v>354.235567673338</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>5.14</v>
+        <v>47</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.90634055347109</v>
+        <v>50.24567038113121</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.82744940278803</v>
+        <v>18.95285157947238</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5939584495713812</v>
+        <v>0.6474599746208418</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0056368482848247</v>
+        <v>0.6722167692830479</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8076</v>
+        <v>8367</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>307.3080618422586</v>
+        <v>352.7371134701024</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>23.4</v>
+        <v>40.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.16207697194211</v>
+        <v>49.91990414773871</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7.383029588730413</v>
+        <v>27.67162689644359</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9687190432221791</v>
+        <v>0.2954830152531132</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0658988141642235</v>
+        <v>0.037612645266911</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>9110</v>
+        <v>8131</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>306.9202840794592</v>
+        <v>344.9807687420521</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>3.14</v>
+        <v>63.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.83949082815286</v>
+        <v>48.19884170385044</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6.857020698163712</v>
+        <v>7.927362906756615</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2251067146519147</v>
+        <v>0.5302667811803669</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0367172125980619</v>
+        <v>0.2934279106583619</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8059</v>
+        <v>9802</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>305.3403265977319</v>
+        <v>342.2240441062062</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>14.15</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.6481185505399</v>
+        <v>49.27828952322293</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20.83308060398981</v>
+        <v>11.10303479292798</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.958289405857469</v>
+        <v>0.2720984716051863</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.07668414414756659</v>
+        <v>0.2486808142526829</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8291</v>
+        <v>8096</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>299.0759753956703</v>
+        <v>340.9003907292991</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>36.1</v>
+        <v>110</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.20187305740293</v>
+        <v>40.35029755008575</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12.02438361736552</v>
+        <v>23.96106816198327</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.078863062023327</v>
+        <v>0.7335143057935072</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0945916122322276</v>
+        <v>-0.2555578560450797</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8102</v>
+        <v>9904</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>290.1626807075692</v>
+        <v>340.7806306431189</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>66.5</v>
+        <v>24.8</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.73426698658709</v>
+        <v>53.22960305551771</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10.90831182782604</v>
+        <v>20.31354319524205</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5221751103001329</v>
+        <v>0.6276287001956103</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.2921906072161579</v>
+        <v>0.09805056816133</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8472</v>
+        <v>8080</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>290.0589919535715</v>
+        <v>335.4888240288068</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>28</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>37.74855347571594</v>
+        <v>51.45673145800725</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.29160253984012</v>
+        <v>52.72299806761597</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.829082562903537</v>
+        <v>0.0452113766954266</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1240591287243104</v>
+        <v>0.0109362985847128</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8163</v>
+        <v>8183</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>288.7306218873344</v>
+        <v>333.5809977946423</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>31.55</v>
+        <v>29.2</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.30944110197373</v>
+        <v>43.56149582264798</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.98381634329948</v>
+        <v>21.13929650784966</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6148577139989552</v>
+        <v>1.171596544242988</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2503726266455356</v>
+        <v>0.0457797251951823</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8201</v>
+        <v>9103</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>274.5435689840262</v>
+        <v>329.8262021796367</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>11.9</v>
+        <v>5.14</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.77143856947193</v>
+        <v>46.9063405958987</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.22465919879261</v>
+        <v>11.82744940261302</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.422008691192745</v>
+        <v>0.5939584495713812</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0477404614858673</v>
+        <v>-0.0056368482981806</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8478</v>
+        <v>8455</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>272.8402760812414</v>
+        <v>322.7554050123621</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>144.5</v>
+        <v>23.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45.68769131364516</v>
+        <v>42.71845464792183</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.48669477963612</v>
+        <v>10.70912306363394</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5002883307443348</v>
+        <v>0.3760211323876402</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.2216152636293857</v>
+        <v>0.08305409157052999</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8411</v>
+        <v>8423</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>271.5336237459164</v>
+        <v>319.3088743010576</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.85</v>
+        <v>17.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.43426297084384</v>
+        <v>51.06580277625715</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14.75230773345522</v>
+        <v>17.28787187374053</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4440691535026352</v>
+        <v>0.2906175812313882</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0383785642218991</v>
+        <v>0.0010610642981397</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8488</v>
+        <v>8076</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>271.0643141972068</v>
+        <v>307.3080618422585</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>23.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.81085209427983</v>
+        <v>48.16207693595391</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.3619940509793</v>
+        <v>7.38302960343419</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.1761897210916715</v>
+        <v>0.9687190432221791</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0237204286676627</v>
+        <v>0.0658988141451443</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9802</v>
+        <v>9110</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>267.2240441062062</v>
+        <v>306.9202840794592</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.27828952322293</v>
+        <v>51.83949084104498</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.10303490124024</v>
+        <v>6.857020715117258</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.2720984716051863</v>
+        <v>0.2251067146519147</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.248680814443488</v>
+        <v>0.0367172125980619</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8089</v>
+        <v>8045</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>265.4296090933857</v>
+        <v>296.3313014583142</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18.15</v>
+        <v>52.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.46878660133761</v>
+        <v>45.34669978550118</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.268475867325879</v>
+        <v>15.02938660995592</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.037757964827823</v>
+        <v>0.6147176075130648</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0808590867759913</v>
+        <v>0.2689598987552846</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8101</v>
+        <v>8488</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>259.7149329899365</v>
+        <v>291.0643141972068</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>12.8</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.03311813385507</v>
+        <v>47.8108456422089</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>9.355164511400609</v>
+        <v>17.36199276258347</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5714932989936568</v>
+        <v>0.1761897210916715</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.4017465718200976</v>
+        <v>-0.0237204265116846</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8210</v>
+        <v>8102</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>258.1766869378258</v>
+        <v>290.1626807075693</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>960</v>
+        <v>66.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>39.43935096652805</v>
+        <v>50.73426699537483</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>18.83153923287336</v>
+        <v>10.90831178306418</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.018543277778091</v>
+        <v>0.5221751103001329</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0545146393594819</v>
+        <v>-0.2921906076549949</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8383</v>
+        <v>8472</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>258.1570475092663</v>
+        <v>290.0589919535715</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>47.58501600917354</v>
+        <v>37.74855638995143</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.14530617196375</v>
+        <v>17.29160255518691</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.340572038769848</v>
+        <v>1.829082562903537</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.3440503366731691</v>
+        <v>0.1240591231531367</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8050</v>
+        <v>8201</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>252.157497633318</v>
+        <v>274.5435689840263</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>57.3</v>
+        <v>11.9</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46.72626757205649</v>
+        <v>47.77143856947193</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11.99317882836869</v>
+        <v>20.22465921648692</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.1957347362151277</v>
+        <v>1.422008691192745</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.3809822953820561</v>
+        <v>0.0477404614572506</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8070</v>
+        <v>8411</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>250.2207512573885</v>
+        <v>271.5336237459164</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>50.7</v>
+        <v>12.85</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.64855622269003</v>
+        <v>50.43426295102006</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.86834568304436</v>
+        <v>14.75230757867829</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4626122151928001</v>
+        <v>0.4440691535026352</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.3206437681315329</v>
+        <v>-0.038378564212361</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8072</v>
+        <v>8070</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>250.1921145877081</v>
+        <v>270.2207512573885</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>26.4</v>
+        <v>50.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.97662718788615</v>
+        <v>53.64855632003764</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.87314096835548</v>
+        <v>15.86834568217885</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.706313421476179</v>
+        <v>0.4626122151928001</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0650386962565553</v>
+        <v>0.3206437678357954</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8114</v>
+        <v>8072</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>246.5014470930924</v>
+        <v>270.1921145877081</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>197.5</v>
+        <v>26.4</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.58389477843048</v>
+        <v>45.9766278852357</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.62544356362991</v>
+        <v>18.87314105772399</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3600097490721252</v>
+        <v>0.706313421476179</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.629630030798678</v>
+        <v>0.06503869564601381</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8227</v>
+        <v>8114</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>245.0644796846108</v>
+        <v>266.5014470930924</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>160</v>
+        <v>197.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>52.2487443339255</v>
+        <v>43.58389463625288</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>19.07377305627418</v>
+        <v>14.62544357525483</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.430728074841213</v>
+        <v>0.3600097490721252</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>2.739564899106886</v>
+        <v>-1.629630032420405</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8068</v>
+        <v>8089</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>244.1487163133561</v>
+        <v>265.4296090933857</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>17.05</v>
+        <v>18.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.67537542163782</v>
+        <v>46.46878638088597</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.47600944729929</v>
+        <v>8.268476005441199</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.614583593380801</v>
+        <v>1.037757964827823</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0006343674434344</v>
+        <v>0.0808590868046095</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8429</v>
+        <v>8210</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>243.805391466713</v>
+        <v>258.1766869378254</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>6.03</v>
+        <v>960</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.2906419258247</v>
+        <v>39.43935099572154</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9.58326089674998</v>
+        <v>18.83153924579905</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7623829802689525</v>
+        <v>1.018543277778091</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0121135254106409</v>
+        <v>-0.0545146398364764</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8171</v>
+        <v>8050</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>241.9381112009582</v>
+        <v>252.157497633318</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20.05</v>
+        <v>57.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.18127963081751</v>
+        <v>46.72626756895998</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.79177757387976</v>
+        <v>11.99317881440048</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.296275099057571</v>
+        <v>0.1957347362151277</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1024036667995789</v>
+        <v>-0.3809822955156076</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8454</v>
+        <v>8068</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>233.2924115333712</v>
+        <v>244.148716313356</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>255.5</v>
+        <v>17.05</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.29566354752891</v>
+        <v>40.67537538639515</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.875548032533</v>
+        <v>13.47600946179675</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.461701541096203</v>
+        <v>0.614583593380801</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1336575975002563</v>
+        <v>-0.0006343675197525999</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8047</v>
+        <v>8454</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>230.3260780609765</v>
+        <v>233.2924115333712</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>43.9</v>
+        <v>255.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.07754135474299</v>
+        <v>46.29566356263481</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>9.761499670421079</v>
+        <v>11.87554812364476</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5311998612375872</v>
+        <v>0.461701541096203</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.3152267247545613</v>
+        <v>-0.1336575980726628</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8277</v>
+        <v>8047</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>226.0724996544249</v>
+        <v>230.3260780609765</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>8.1</v>
+        <v>43.9</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>47.4489478148783</v>
+        <v>43.07754137872836</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.75621375661736</v>
+        <v>9.761499754266852</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.83238871167104</v>
+        <v>0.5311998612375872</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.045776756875235</v>
+        <v>-0.3152267248117996</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8048</v>
+        <v>8277</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>225.689034340432</v>
+        <v>226.0724996544249</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>52</v>
+        <v>8.1</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.99890439378296</v>
+        <v>47.44894795880658</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.3836919368788</v>
+        <v>9.756213822251969</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4844511384778949</v>
+        <v>1.83238871167104</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>1</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.326984686387457</v>
+        <v>0.0457767568218143</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8044</v>
+        <v>8048</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>218.7345843520417</v>
+        <v>225.689034340432</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>24.45</v>
+        <v>52</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>33.79384785353068</v>
+        <v>43.9989044394847</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.83363477257175</v>
+        <v>14.38369206219406</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.752619318178742</v>
+        <v>0.4844511384778949</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1444416786054381</v>
+        <v>0.3269846862252816</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8049</v>
+        <v>8044</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>214.8781906725223</v>
+        <v>218.7345843520416</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>24.5</v>
+        <v>24.45</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>33.38122961675963</v>
+        <v>33.79384781153929</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.69804198617844</v>
+        <v>13.83363484450608</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3448436224811586</v>
+        <v>1.752619318178742</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1130082772941217</v>
+        <v>-0.1444416786912972</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8176</v>
+        <v>8049</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>209.6302074237566</v>
+        <v>214.8781906725223</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>9.85</v>
+        <v>24.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.20527833300485</v>
+        <v>33.3812296244226</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.37636874710916</v>
+        <v>21.69804203514438</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4218516981294099</v>
+        <v>0.3448436224811586</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0090999093842292</v>
+        <v>-0.1130082773609004</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8477</v>
+        <v>8176</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>206.3687398194516</v>
+        <v>209.6302074237566</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15.45</v>
+        <v>9.85</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>49.14544226652198</v>
+        <v>45.20527838148374</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>4.561580762675815</v>
+        <v>18.37636881403296</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6770813268097238</v>
+        <v>0.4218516981294099</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0104814187312541</v>
+        <v>-0.0090999094223887</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8045</v>
+        <v>8477</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>186.3313014583141</v>
+        <v>206.3687398194516</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>52.5</v>
+        <v>15.45</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.34669977645469</v>
+        <v>49.14544230083054</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.0293865955157</v>
+        <v>4.561580842663558</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6147176075130648</v>
+        <v>0.6770813268097238</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,11 +6135,11 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.2689598991177984</v>
+        <v>-0.0104814187884915</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.99367150675939</v>
+        <v>36.99367158512688</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.7485859525437</v>
+        <v>21.74858584592625</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.4216788331822317</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.05111991828729</v>
+        <v>-0.0511199186211801</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8341</v>
+        <v>8940</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>167.2824068216571</v>
+        <v>169.7488461019041</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>49.9849687890748</v>
+        <v>39.65185739312063</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.81422042225295</v>
+        <v>14.40218285815561</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.072874207951198</v>
+        <v>1.284840209678068</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0915960127366187</v>
+        <v>0.0332985621333982</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8466</v>
+        <v>8476</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>163.1853641914488</v>
+        <v>169.1241308855281</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>15.8</v>
+        <v>19.85</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.6989849236792</v>
+        <v>42.32931184265931</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>26.84833129298157</v>
+        <v>12.13467523816677</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7662915350740626</v>
+        <v>0.928437918592134</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0457572867121417</v>
+        <v>0.0454357379136912</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8940</v>
+        <v>8341</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>149.7488461019041</v>
+        <v>167.2824068216571</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>15.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.651857583396</v>
+        <v>49.9849687763416</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.4021827030503</v>
+        <v>11.81422038090418</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.284840209678068</v>
+        <v>1.072874207951198</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0332985621333982</v>
+        <v>0.0915960125649032</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8476</v>
+        <v>8466</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>149.1241308855281</v>
+        <v>163.1853641914488</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>19.85</v>
+        <v>15.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.32931187445622</v>
+        <v>41.69898473901217</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.13467522749834</v>
+        <v>26.84833137634309</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.928437918592134</v>
+        <v>0.7662915350740626</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,11 +6400,11 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.045435737942309</v>
+        <v>-0.045757286664442</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>148.6423749592632</v>
+        <v>148.6423749592633</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>93.8</v>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.51682332855548</v>
+        <v>38.51682337150446</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.21870961809844</v>
+        <v>11.21870962141591</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.4025347911420118</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.250286604205518</v>
+        <v>-0.2502866049686871</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>144.7807903037574</v>
+        <v>144.7807903037573</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>26.1</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>49.23366238530839</v>
+        <v>49.23366241110857</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.972408724444093</v>
+        <v>7.97240867115029</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.2209475785271562</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.08612049886364199</v>
+        <v>0.086120498634686</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>34.86197336064428</v>
+        <v>34.86197337742709</v>
       </c>
       <c r="I115" s="2" t="n">
         <v>15.21711956177239</v>
@@ -6550,7 +6550,7 @@
         <v>1.42475805218782</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1074042035248699</v>
+        <v>0.1074042034867215</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.99404432861653</v>
+        <v>44.99404438667148</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>8.212686804142608</v>
+        <v>8.21268686752493</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.910828999694096</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.07111429223646359</v>
+        <v>-0.0711142923223219</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>47.32013227769664</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.66472248905906</v>
+        <v>18.6647225039477</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.6278030154339455</v>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>112.9581232058305</v>
+        <v>112.9581232058303</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>159</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>36.20688389555878</v>
+        <v>36.20688384961183</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.36786721995633</v>
+        <v>18.367867372092</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.611115296788297</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.4678574912329738</v>
+        <v>-0.4678574908513981</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
